--- a/Source data/Fig.3D.xlsx
+++ b/Source data/Fig.3D.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GITHUB\HGT_and_fitness\Source data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\HGT_and_fitness\Source data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC003CFC-B189-498D-8847-B61C9210EFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A7429A-18D4-4750-902B-3B27536963E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14055" yWindow="4275" windowWidth="16140" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5560" yWindow="1970" windowWidth="19200" windowHeight="10050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="correlate" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>p-value</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>t0</t>
-  </si>
-  <si>
-    <t>Distance_to_root</t>
   </si>
   <si>
     <t>#2</t>
@@ -152,7 +149,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Spearman correlation to root-to-tip distance</t>
+    <t>Distance_to_root (100% core genes)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Distance_to_root (genome contents)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spearman correlation to root-to-tip distance (100% core genes)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spearman correlation to root-to-tip distance (genome contents)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -532,51 +541,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1">
-        <v>-0.14649999999999999</v>
+        <v>-0.50860000000000005</v>
       </c>
       <c r="C1" s="1">
-        <v>-0.4113</v>
+        <v>-0.29949999999999999</v>
       </c>
       <c r="D1" s="1">
-        <v>-0.3967</v>
+        <v>-0.51090000000000002</v>
       </c>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="F1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1">
+        <v>-9.8599999999999993E-2</v>
+      </c>
+      <c r="H1" s="1">
+        <v>-0.39589999999999997</v>
+      </c>
+      <c r="I1" s="1">
+        <v>-0.40050000000000002</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>0.39400000000000002</v>
+        <v>1.5299999999999999E-3</v>
       </c>
       <c r="C2" s="1">
-        <v>1.2699999999999999E-2</v>
+        <v>7.5899999999999995E-2</v>
       </c>
       <c r="D2" s="1">
-        <v>1.66E-2</v>
+        <v>1.4499999999999999E-3</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="F2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.56730000000000003</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -588,15 +615,17 @@
         <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>0.52708128200000004</v>
@@ -608,15 +637,17 @@
         <v>6.0870257560000001</v>
       </c>
       <c r="E4" s="1">
-        <v>6.2865799E-2</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>4.43206822999999E-2</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.46246999999999999</v>
+      </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1">
         <v>9.4372301000000006E-2</v>
@@ -628,15 +659,17 @@
         <v>-4.2096154869999998</v>
       </c>
       <c r="E5" s="1">
-        <v>7.2596068999999999E-2</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>4.8998357099999897E-2</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.56838999999999995</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
         <v>8.6587167000000007E-2</v>
@@ -648,15 +681,17 @@
         <v>-3.2734141769999998</v>
       </c>
       <c r="E6" s="1">
-        <v>6.4987239000000002E-2</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>4.62863421999999E-2</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.47981000000000001</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1">
         <v>0.46083241000000003</v>
@@ -668,15 +703,17 @@
         <v>4.7416654730000003</v>
       </c>
       <c r="E7" s="1">
-        <v>5.3066308999999999E-2</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>4.3596416699999897E-2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.41276000000000002</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1">
         <v>0.45248054199999999</v>
@@ -688,15 +725,17 @@
         <v>5.318364248</v>
       </c>
       <c r="E8" s="1">
-        <v>5.4690252000000002E-2</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>4.42768206999999E-2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.4597</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1">
         <v>0.42286677099999997</v>
@@ -708,15 +747,17 @@
         <v>5.4264607790000001</v>
       </c>
       <c r="E9" s="1">
-        <v>5.1052725E-2</v>
-      </c>
-      <c r="F9" s="1"/>
+        <v>4.4208981299999901E-2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.367619999999999</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1">
         <v>0.47077870700000002</v>
@@ -728,15 +769,17 @@
         <v>6.0319052089999996</v>
       </c>
       <c r="E10" s="1">
-        <v>6.3096339000000001E-2</v>
-      </c>
-      <c r="F10" s="1"/>
+        <v>4.4702981899999897E-2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.48703000000000002</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1">
         <v>0.26951857299999998</v>
@@ -748,15 +791,17 @@
         <v>4.7229174110000001</v>
       </c>
       <c r="E11" s="1">
-        <v>5.3070272000000002E-2</v>
-      </c>
-      <c r="F11" s="1"/>
+        <v>4.4231836299999903E-2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.39690999999999999</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1">
         <v>0.398376077</v>
@@ -768,15 +813,17 @@
         <v>6.2604934940000003</v>
       </c>
       <c r="E12" s="1">
-        <v>4.9811194000000003E-2</v>
-      </c>
-      <c r="F12" s="1"/>
+        <v>4.42368309999999E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.397259999999999</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1">
         <v>0.31672844</v>
@@ -788,15 +835,17 @@
         <v>6.1627753839999997</v>
       </c>
       <c r="E13" s="1">
-        <v>5.1115784999999997E-2</v>
-      </c>
-      <c r="F13" s="1"/>
+        <v>4.4209500299999899E-2</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.382989999999999</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1">
         <v>0.430729109</v>
@@ -808,15 +857,17 @@
         <v>5.7363604229999998</v>
       </c>
       <c r="E14" s="1">
-        <v>5.0256139999999998E-2</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>4.4237675399999898E-2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.39727999999999902</v>
+      </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1">
         <v>0.425495595</v>
@@ -828,15 +879,17 @@
         <v>5.8304778449999999</v>
       </c>
       <c r="E15" s="1">
-        <v>4.9355700000000002E-2</v>
-      </c>
-      <c r="F15" s="1"/>
+        <v>4.4237675399999898E-2</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.39720999999999901</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1">
         <v>0.42464349000000001</v>
@@ -848,15 +901,17 @@
         <v>5.9980094409999998</v>
       </c>
       <c r="E16" s="1">
-        <v>5.3639892000000002E-2</v>
-      </c>
-      <c r="F16" s="1"/>
+        <v>4.4230719599999899E-2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.40305999999999997</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1">
         <v>0.41828817400000001</v>
@@ -868,15 +923,17 @@
         <v>6.1692978319999998</v>
       </c>
       <c r="E17" s="1">
-        <v>5.1202235999999998E-2</v>
-      </c>
-      <c r="F17" s="1"/>
+        <v>4.4230087099999899E-2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.37322999999999901</v>
+      </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1">
         <v>0.40324247499999999</v>
@@ -888,15 +945,17 @@
         <v>5.641535266</v>
       </c>
       <c r="E18" s="1">
-        <v>4.2886972000000002E-2</v>
-      </c>
-      <c r="F18" s="1"/>
+        <v>4.4859903299999997E-2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.37534000000000001</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="1">
         <v>7.3828933999999999E-2</v>
@@ -908,15 +967,17 @@
         <v>-4.9717973840000003</v>
       </c>
       <c r="E19" s="1">
-        <v>6.6890988999999998E-2</v>
-      </c>
-      <c r="F19" s="1"/>
+        <v>4.6285879599999899E-2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0.45032</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B20" s="1">
         <v>0.40121377800000002</v>
@@ -928,15 +989,17 @@
         <v>4.9063353469999997</v>
       </c>
       <c r="E20" s="1">
-        <v>5.7056752000000002E-2</v>
-      </c>
-      <c r="F20" s="1"/>
+        <v>4.4857856299999901E-2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.39348</v>
+      </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="1">
         <v>0.38439710799999999</v>
@@ -948,15 +1011,17 @@
         <v>5.24857934</v>
       </c>
       <c r="E21" s="1">
-        <v>5.4035558999999997E-2</v>
-      </c>
-      <c r="F21" s="1"/>
+        <v>4.4175191899999897E-2</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0.40394999999999998</v>
+      </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B22" s="1">
         <v>0.38178199899999998</v>
@@ -968,15 +1033,17 @@
         <v>5.9142963609999999</v>
       </c>
       <c r="E22" s="1">
-        <v>5.2273728999999998E-2</v>
-      </c>
-      <c r="F22" s="1"/>
+        <v>4.3596416699999897E-2</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.40739999999999998</v>
+      </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
     </row>
-    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B23" s="1">
         <v>0.405959721</v>
@@ -988,15 +1055,17 @@
         <v>6.3675738300000004</v>
       </c>
       <c r="E23" s="1">
-        <v>5.1072859999999998E-2</v>
-      </c>
-      <c r="F23" s="1"/>
+        <v>4.4208981299999901E-2</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0.37592999999999999</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
     </row>
-    <row r="24" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B24" s="1">
         <v>0.401079399</v>
@@ -1008,15 +1077,17 @@
         <v>6.044469265</v>
       </c>
       <c r="E24" s="1">
-        <v>4.7830042000000003E-2</v>
-      </c>
-      <c r="F24" s="1"/>
+        <v>4.4233954699999897E-2</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0.370109999999999</v>
+      </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="1">
         <v>0.30856376400000002</v>
@@ -1028,15 +1099,17 @@
         <v>5.6266648469999998</v>
       </c>
       <c r="E25" s="1">
-        <v>5.2579642000000003E-2</v>
-      </c>
-      <c r="F25" s="1"/>
+        <v>4.4853376899999901E-2</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0.39821000000000001</v>
+      </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="1">
         <v>0.36195446599999997</v>
@@ -1048,15 +1121,17 @@
         <v>5.4795900619999998</v>
       </c>
       <c r="E26" s="1">
-        <v>5.0297831000000001E-2</v>
-      </c>
-      <c r="F26" s="1"/>
+        <v>4.3969485799999902E-2</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0.38170999999999999</v>
+      </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="1">
         <v>0.47129681299999998</v>
@@ -1068,15 +1143,17 @@
         <v>5.4342506730000002</v>
       </c>
       <c r="E27" s="1">
-        <v>5.7409791000000002E-2</v>
-      </c>
-      <c r="F27" s="1"/>
+        <v>4.3886867699999901E-2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0.41808000000000001</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="1">
         <v>0.36734769699999997</v>
@@ -1088,15 +1165,17 @@
         <v>5.7076993470000001</v>
       </c>
       <c r="E28" s="1">
-        <v>4.8376531E-2</v>
-      </c>
-      <c r="F28" s="1"/>
+        <v>4.4007985699999898E-2</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0.38207000000000002</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="1">
         <v>0.483505833</v>
@@ -1108,15 +1187,17 @@
         <v>6.3647722010000001</v>
       </c>
       <c r="E29" s="1">
-        <v>4.5711781E-2</v>
-      </c>
-      <c r="F29" s="1"/>
+        <v>4.3893144599999899E-2</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0.38800000000000001</v>
+      </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="1">
         <v>0.39848552500000001</v>
@@ -1128,15 +1209,17 @@
         <v>5.6796178890000002</v>
       </c>
       <c r="E30" s="1">
-        <v>4.5465000999999998E-2</v>
-      </c>
-      <c r="F30" s="1"/>
+        <v>4.3892416999999899E-2</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0.36771999999999999</v>
+      </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="1">
         <v>0.48297580899999998</v>
@@ -1148,15 +1231,17 @@
         <v>7.115268586</v>
       </c>
       <c r="E31" s="1">
-        <v>8.3495171000000007E-2</v>
-      </c>
-      <c r="F31" s="1"/>
+        <v>4.38088494999999E-2</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0.46500999999999998</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="1">
         <v>0.44624339499999999</v>
@@ -1168,15 +1253,17 @@
         <v>5.8380371719999999</v>
       </c>
       <c r="E32" s="1">
-        <v>6.1441260999999997E-2</v>
-      </c>
-      <c r="F32" s="1"/>
+        <v>4.3886942699999897E-2</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0.42642000000000002</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="1">
         <v>0.46164763599999997</v>
@@ -1188,15 +1275,17 @@
         <v>7.4526841040000003</v>
       </c>
       <c r="E33" s="1">
-        <v>5.7059387000000003E-2</v>
-      </c>
-      <c r="F33" s="1"/>
+        <v>4.43015885999999E-2</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0.40776000000000001</v>
+      </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="1">
         <v>0.39111567200000003</v>
@@ -1208,15 +1297,17 @@
         <v>6.1178631010000002</v>
       </c>
       <c r="E34" s="1">
-        <v>4.7620497999999997E-2</v>
-      </c>
-      <c r="F34" s="1"/>
+        <v>4.3954226799999899E-2</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0.34788999999999998</v>
+      </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="1">
         <v>0.48190231300000003</v>
@@ -1228,15 +1319,17 @@
         <v>6.5900037459999998</v>
       </c>
       <c r="E35" s="1">
-        <v>5.0192021000000003E-2</v>
-      </c>
-      <c r="F35" s="1"/>
+        <v>4.3898406799999901E-2</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0.39085999999999999</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" s="1">
         <v>0.120176399</v>
@@ -1248,15 +1341,17 @@
         <v>-8.7053010000000004E-3</v>
       </c>
       <c r="E36" s="1">
-        <v>7.1335688999999994E-2</v>
-      </c>
-      <c r="F36" s="1"/>
+        <v>4.6194792899999899E-2</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.47744999999999999</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B37" s="1">
         <v>8.1522686999999996E-2</v>
@@ -1268,15 +1363,17 @@
         <v>-3.0954975220000001</v>
       </c>
       <c r="E37" s="1">
-        <v>5.9839538999999997E-2</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>4.5497864499999902E-2</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0.45599000000000001</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B38" s="1">
         <v>8.7715506999999998E-2</v>
@@ -1288,15 +1385,17 @@
         <v>-4.4327814639999996</v>
       </c>
       <c r="E38" s="1">
-        <v>5.5773758999999999E-2</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>4.5518043499999897E-2</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0.44903999999999999</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B39" s="1">
         <v>8.9752283000000002E-2</v>
@@ -1308,9 +1407,11 @@
         <v>-2.4322415739999999</v>
       </c>
       <c r="E39" s="1">
-        <v>5.9811758999999999E-2</v>
-      </c>
-      <c r="F39" s="1"/>
+        <v>4.5537514399999902E-2</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0.47099999999999997</v>
+      </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
